--- a/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por empastes</t>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 28,36</t>
+          <t>13,43; 29,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 23,0</t>
+          <t>9,02; 23,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,02; 31,08</t>
+          <t>14,18; 30,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 26,6</t>
+          <t>12,58; 27,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 25,58</t>
+          <t>11,6; 25,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 32,77</t>
+          <t>16,6; 33,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 23,82</t>
+          <t>9,47; 23,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 21,34</t>
+          <t>6,2; 21,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 25,14</t>
+          <t>15,03; 24,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 25,75</t>
+          <t>14,21; 25,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,09</t>
+          <t>13,53; 25,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,97</t>
+          <t>10,41; 21,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,48; 33,68</t>
+          <t>20,01; 32,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 34,95</t>
+          <t>21,39; 34,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,96; 27,3</t>
+          <t>14,7; 27,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 18,47</t>
+          <t>7,97; 18,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,06</t>
+          <t>13,22; 24,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 30,66</t>
+          <t>17,15; 29,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 30,2</t>
+          <t>17,11; 30,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,43</t>
+          <t>13,2; 24,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 27,42</t>
+          <t>17,97; 26,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 30,48</t>
+          <t>21,42; 30,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 26,45</t>
+          <t>17,45; 26,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 20,3</t>
+          <t>12,54; 20,86</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 31,15</t>
+          <t>14,84; 30,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 25,81</t>
+          <t>11,18; 24,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 24,2</t>
+          <t>10,2; 23,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 35,56</t>
+          <t>18,67; 36,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 22,96</t>
+          <t>10,61; 23,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 29,35</t>
+          <t>14,81; 29,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 31,85</t>
+          <t>15,28; 32,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 25,15</t>
+          <t>11,56; 25,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 24,39</t>
+          <t>13,81; 23,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 25,09</t>
+          <t>14,73; 24,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 25,52</t>
+          <t>14,87; 25,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,45; 27,71</t>
+          <t>16,18; 27,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 21,31</t>
+          <t>8,68; 21,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 26,79</t>
+          <t>12,72; 26,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 17,48</t>
+          <t>6,66; 17,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 19,56</t>
+          <t>8,65; 20,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 25,01</t>
+          <t>10,99; 24,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,71</t>
+          <t>5,17; 15,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 17,1</t>
+          <t>6,79; 17,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 22,03</t>
+          <t>9,18; 22,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 20,36</t>
+          <t>11,04; 19,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 18,28</t>
+          <t>9,73; 18,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,57</t>
+          <t>7,8; 14,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 18,7</t>
+          <t>10,11; 18,34</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,45</t>
+          <t>17,59; 24,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,13</t>
+          <t>17,28; 24,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,23</t>
+          <t>13,99; 20,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,23</t>
+          <t>14,41; 21,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,63</t>
+          <t>14,43; 21,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,91</t>
+          <t>15,88; 22,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,83</t>
+          <t>14,87; 21,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,8</t>
+          <t>13,49; 19,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,81</t>
+          <t>16,96; 21,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,31</t>
+          <t>17,62; 22,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,38; 19,96</t>
+          <t>15,58; 20,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,27</t>
+          <t>14,4; 19,4</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15581</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15489</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13027</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18106</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10733</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30476</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29469</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27241</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>23760</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10161; 22453</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6671; 17152</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10045; 21437</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8773; 18953</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9535; 20818</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12493; 24851</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7248; 18102</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5285; 18319</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>23723; 39258</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>21200; 37987</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19948; 37301</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>16131; 33296</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>28861</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31204</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22019</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14769</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27035</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25040</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>30606</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>49631</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>58239</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47059</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>45375</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22019; 36260</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23947; 38556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15757; 29580</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9066; 21530</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14755; 27293</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19771; 34545</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18577; 32831</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>22097; 41160</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>39841; 59500</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>48670; 68963</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>37658; 56888</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>35244; 58634</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13106</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27746</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17008</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18169</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>21221</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27726</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30113</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30269</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>48967</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10268; 21212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8331; 18450</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7712; 17963</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19963; 38643</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8259; 18464</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11814; 23846</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11744; 25072</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13900; 30283</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20307; 35258</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22722; 38509</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22672; 38418</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>36765; 62760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17272</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13364</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15205</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8971</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16228</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28427</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26243</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24152</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>29593</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8334; 20459</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11826; 24187</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7254; 18774</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8750; 20842</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9898; 21939</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4978; 14809</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7248; 18367</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10244; 25039</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20534; 36953</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18415; 34988</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16838; 32115</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>21515; 39012</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>72789</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72944</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>68906</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>78788</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>136260</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144064</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>147694</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>61716; 87218</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>61062; 85384</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>50723; 73943</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56430; 84026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>52195; 76163</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>58221; 83474</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>54839; 79158</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>65330; 96364</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>120886; 152067</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>126829; 162877</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>113958; 147795</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>126168; 169935</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 29,67</t>
+          <t>13,46; 28,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 23,2</t>
+          <t>9,89; 22,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 30,26</t>
+          <t>14,7; 30,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 27,17</t>
+          <t>12,11; 26,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 25,33</t>
+          <t>12,0; 26,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 33,03</t>
+          <t>16,07; 32,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 23,65</t>
+          <t>9,43; 23,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 21,49</t>
+          <t>6,31; 21,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 24,87</t>
+          <t>14,56; 24,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 25,47</t>
+          <t>14,21; 25,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,31</t>
+          <t>13,36; 24,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 21,48</t>
+          <t>10,17; 21,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,01; 32,95</t>
+          <t>20,16; 32,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,39; 34,44</t>
+          <t>21,86; 34,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 27,6</t>
+          <t>14,49; 26,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 18,93</t>
+          <t>7,81; 18,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 24,45</t>
+          <t>13,18; 25,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 29,97</t>
+          <t>17,25; 30,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 30,23</t>
+          <t>16,81; 30,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 24,59</t>
+          <t>13,75; 24,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 26,84</t>
+          <t>18,27; 26,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,42; 30,35</t>
+          <t>21,16; 30,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 26,36</t>
+          <t>17,67; 26,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,86</t>
+          <t>12,94; 20,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 30,65</t>
+          <t>14,68; 29,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,18; 24,77</t>
+          <t>11,65; 25,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 23,76</t>
+          <t>10,58; 24,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 36,13</t>
+          <t>18,67; 36,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 23,71</t>
+          <t>10,58; 24,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,81; 29,9</t>
+          <t>14,55; 29,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 32,62</t>
+          <t>15,72; 32,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 25,18</t>
+          <t>11,3; 24,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 23,97</t>
+          <t>14,37; 24,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 24,97</t>
+          <t>14,88; 25,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,87; 25,2</t>
+          <t>14,79; 25,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 27,62</t>
+          <t>16,81; 27,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 21,31</t>
+          <t>8,84; 20,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 26,01</t>
+          <t>12,7; 26,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 17,22</t>
+          <t>6,46; 16,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 20,6</t>
+          <t>7,94; 19,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 24,36</t>
+          <t>10,73; 23,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,38</t>
+          <t>5,4; 15,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 17,2</t>
+          <t>6,76; 17,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 22,44</t>
+          <t>8,71; 22,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 19,86</t>
+          <t>11,55; 20,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 18,48</t>
+          <t>9,87; 18,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 14,88</t>
+          <t>7,9; 15,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 18,34</t>
+          <t>9,73; 18,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,85</t>
+          <t>17,8; 24,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,16</t>
+          <t>17,13; 24,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,39</t>
+          <t>14,16; 20,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,46</t>
+          <t>14,03; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,06</t>
+          <t>14,62; 20,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,77</t>
+          <t>16,33; 22,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 21,47</t>
+          <t>15,14; 21,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,89</t>
+          <t>13,07; 19,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,34</t>
+          <t>16,79; 21,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,62</t>
+          <t>17,47; 22,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,21</t>
+          <t>15,39; 19,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,4</t>
+          <t>14,79; 19,38</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10161; 22453</t>
+          <t>10185; 21365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6671; 17152</t>
+          <t>7313; 16598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10045; 21437</t>
+          <t>10410; 21869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8773; 18953</t>
+          <t>8449; 18821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9535; 20818</t>
+          <t>9862; 21708</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12493; 24851</t>
+          <t>12091; 24751</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7248; 18102</t>
+          <t>7216; 17702</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5285; 18319</t>
+          <t>5375; 18634</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23723; 39258</t>
+          <t>22986; 38710</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21200; 37987</t>
+          <t>21203; 37981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19948; 37301</t>
+          <t>19695; 35583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16131; 33296</t>
+          <t>15765; 33308</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22019; 36260</t>
+          <t>22187; 36179</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23947; 38556</t>
+          <t>24474; 38915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15757; 29580</t>
+          <t>15535; 28922</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9066; 21530</t>
+          <t>8879; 21498</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14755; 27293</t>
+          <t>14713; 28059</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19771; 34545</t>
+          <t>19889; 34736</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18577; 32831</t>
+          <t>18255; 32990</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22097; 41160</t>
+          <t>23010; 41103</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39841; 59500</t>
+          <t>40498; 59709</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48670; 68963</t>
+          <t>48082; 68762</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37658; 56888</t>
+          <t>38123; 57514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35244; 58634</t>
+          <t>36381; 57247</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10268; 21212</t>
+          <t>10159; 20644</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8331; 18450</t>
+          <t>8680; 18992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7712; 17963</t>
+          <t>8000; 18478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19963; 38643</t>
+          <t>19964; 39210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8259; 18464</t>
+          <t>8239; 19163</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11814; 23846</t>
+          <t>11602; 23296</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11744; 25072</t>
+          <t>12086; 24762</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13900; 30283</t>
+          <t>13584; 29932</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20307; 35258</t>
+          <t>21135; 35343</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22722; 38509</t>
+          <t>22948; 38946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22672; 38418</t>
+          <t>22544; 38807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36765; 62760</t>
+          <t>38196; 63035</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8334; 20459</t>
+          <t>8484; 20083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11826; 24187</t>
+          <t>11808; 24363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7254; 18774</t>
+          <t>7043; 18361</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8750; 20842</t>
+          <t>8038; 19709</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9898; 21939</t>
+          <t>9660; 21352</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4978; 14809</t>
+          <t>5205; 14716</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7248; 18367</t>
+          <t>7222; 18754</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10244; 25039</t>
+          <t>9719; 24632</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20534; 36953</t>
+          <t>21485; 37894</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18415; 34988</t>
+          <t>18685; 34922</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16838; 32115</t>
+          <t>17047; 32555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21515; 39012</t>
+          <t>20694; 38845</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61716; 87218</t>
+          <t>62455; 85858</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61062; 85384</t>
+          <t>60546; 84849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50723; 73943</t>
+          <t>51337; 73260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56430; 84026</t>
+          <t>54937; 82922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52195; 76163</t>
+          <t>52878; 75264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58221; 83474</t>
+          <t>59864; 83812</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54839; 79158</t>
+          <t>55840; 81047</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65330; 96364</t>
+          <t>63316; 94934</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120886; 152067</t>
+          <t>119633; 152819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126829; 162877</t>
+          <t>125795; 161024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113958; 147795</t>
+          <t>112577; 145356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126168; 169935</t>
+          <t>129528; 169743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20,59%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>21,86%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 28,23</t>
+          <t>11,76; 25,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 22,45</t>
+          <t>16,11; 32,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 30,87</t>
+          <t>9,5; 23,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 26,98</t>
+          <t>6,5; 21,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 26,41</t>
+          <t>13,81; 28,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 32,9</t>
+          <t>8,93; 23,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 23,13</t>
+          <t>15,02; 31,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 21,86</t>
+          <t>11,61; 26,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 24,52</t>
+          <t>14,54; 25,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 25,46</t>
+          <t>14,62; 25,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 24,14</t>
+          <t>13,26; 24,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 21,49</t>
+          <t>10,52; 21,06</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,54%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 32,87</t>
+          <t>13,18; 25,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,86; 34,76</t>
+          <t>17,76; 30,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 26,98</t>
+          <t>16,94; 30,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 18,9</t>
+          <t>12,55; 23,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,14</t>
+          <t>20,48; 33,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 30,13</t>
+          <t>21,8; 34,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 30,38</t>
+          <t>14,96; 27,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 24,56</t>
+          <t>7,83; 18,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 26,93</t>
+          <t>17,93; 27,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 30,26</t>
+          <t>21,37; 30,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 26,65</t>
+          <t>17,61; 26,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 20,36</t>
+          <t>11,65; 19,46</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>21,85%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 29,83</t>
+          <t>10,55; 22,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,65; 25,49</t>
+          <t>15,1; 29,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 24,45</t>
+          <t>16,47; 31,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 36,66</t>
+          <t>11,22; 25,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 24,61</t>
+          <t>15,29; 31,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 29,21</t>
+          <t>11,04; 25,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 32,22</t>
+          <t>10,19; 24,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 24,89</t>
+          <t>17,88; 32,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 24,03</t>
+          <t>14,33; 24,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 25,25</t>
+          <t>14,82; 25,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 25,46</t>
+          <t>14,78; 25,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 27,74</t>
+          <t>16,24; 26,54</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>18,58%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 20,92</t>
+          <t>11,11; 25,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 26,2</t>
+          <t>5,08; 15,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 16,84</t>
+          <t>7,07; 17,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,48</t>
+          <t>7,96; 20,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 23,71</t>
+          <t>8,75; 21,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,28</t>
+          <t>12,65; 26,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 17,57</t>
+          <t>6,89; 17,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 22,08</t>
+          <t>8,6; 19,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,37</t>
+          <t>11,27; 20,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,45</t>
+          <t>9,96; 18,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 15,09</t>
+          <t>8,15; 15,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 18,26</t>
+          <t>9,9; 17,97</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,47</t>
+          <t>14,55; 20,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 24,01</t>
+          <t>15,99; 22,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,2</t>
+          <t>15,31; 21,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 21,17</t>
+          <t>12,59; 19,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,81</t>
+          <t>17,27; 24,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 22,86</t>
+          <t>17,58; 24,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,98</t>
+          <t>13,77; 20,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,6</t>
+          <t>14,04; 20,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 21,44</t>
+          <t>16,81; 21,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,37</t>
+          <t>17,74; 22,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,87</t>
+          <t>15,38; 19,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,38</t>
+          <t>14,34; 18,67</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18106</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10234</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15581</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11363</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15489</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13027</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14895</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18106</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11752</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>23757</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10185; 21365</t>
+          <t>9668; 21025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7313; 16598</t>
+          <t>12122; 24660</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10410; 21869</t>
+          <t>7270; 18236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8449; 18821</t>
+          <t>5294; 17444</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9862; 21708</t>
+          <t>10448; 21463</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12091; 24751</t>
+          <t>6604; 17000</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7216; 17702</t>
+          <t>10639; 22019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5375; 18634</t>
+          <t>8622; 19316</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22986; 38710</t>
+          <t>22947; 39689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21203; 37981</t>
+          <t>21804; 38406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19695; 35583</t>
+          <t>19547; 35511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15765; 33308</t>
+          <t>16378; 32792</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27035</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25040</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28491</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28861</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>31204</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>22019</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14769</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20770</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27035</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25040</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>43403</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22187; 36179</t>
+          <t>14717; 27971</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24474; 38915</t>
+          <t>20472; 35342</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15535; 28922</t>
+          <t>18399; 32796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8879; 21498</t>
+          <t>20380; 38087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14713; 28059</t>
+          <t>22541; 37068</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19889; 34736</t>
+          <t>24407; 39131</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18255; 32990</t>
+          <t>16030; 29259</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23010; 41103</t>
+          <t>9160; 21446</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40498; 59709</t>
+          <t>39743; 60791</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48082; 68762</t>
+          <t>48557; 69259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38123; 57514</t>
+          <t>38000; 57080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36381; 57247</t>
+          <t>32538; 54347</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17008</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18169</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15125</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>13106</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12100</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27746</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12601</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17008</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18169</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>45324</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10159; 20644</t>
+          <t>8219; 17877</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8680; 18992</t>
+          <t>12044; 23407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8000; 18478</t>
+          <t>12657; 24480</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19964; 39210</t>
+          <t>12579; 28710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8239; 19163</t>
+          <t>10582; 21562</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11602; 23296</t>
+          <t>8222; 19230</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12086; 24762</t>
+          <t>7705; 18291</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13584; 29932</t>
+          <t>18312; 33683</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21135; 35343</t>
+          <t>21082; 35879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22948; 38946</t>
+          <t>22853; 38697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22544; 38807</t>
+          <t>22530; 38907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38196; 63035</t>
+          <t>34850; 56942</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15205</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8971</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14059</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13222</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17272</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>12023</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13364</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15205</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8971</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12129</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>27699</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8484; 20083</t>
+          <t>10007; 22523</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11808; 24363</t>
+          <t>4891; 15126</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7043; 18361</t>
+          <t>7550; 18252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8038; 19709</t>
+          <t>8373; 21536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9660; 21352</t>
+          <t>8395; 20458</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5205; 14716</t>
+          <t>11764; 24905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7222; 18754</t>
+          <t>7507; 19053</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9719; 24632</t>
+          <t>8824; 20437</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21485; 37894</t>
+          <t>20972; 37872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18685; 34922</t>
+          <t>18851; 34605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17047; 32555</t>
+          <t>17595; 33595</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20694; 38845</t>
+          <t>20565; 37347</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62455; 85858</t>
+          <t>52631; 74619</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60546; 84849</t>
+          <t>58627; 83973</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51337; 73260</t>
+          <t>56471; 80516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54937; 82922</t>
+          <t>58072; 88226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52878; 75264</t>
+          <t>60600; 85800</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59864; 83812</t>
+          <t>62117; 85259</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55840; 81047</t>
+          <t>49923; 73348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63316; 94934</t>
+          <t>55645; 79711</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119633; 152819</t>
+          <t>119807; 155465</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125795; 161024</t>
+          <t>127695; 160607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112577; 145356</t>
+          <t>112503; 146019</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>129528; 169743</t>
+          <t>122944; 160070</t>
         </is>
       </c>
     </row>
